--- a/논문수치계산.xlsx
+++ b/논문수치계산.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidus\Desktop\GRI Github\Raster_PV_Poten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\Raster_PV_Poten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC84A092-485E-4365-A100-7456CAA7FBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6588776-8C1C-4F90-B47B-19F50E2FA6F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24135" yWindow="0" windowWidth="14370" windowHeight="20985" activeTab="1" xr2:uid="{3A568D68-98E3-4C0A-84A1-4DCCBF5FEC80}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{3A568D68-98E3-4C0A-84A1-4DCCBF5FEC80}"/>
   </bookViews>
   <sheets>
     <sheet name="수정사항" sheetId="6" r:id="rId1"/>
@@ -526,10 +526,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>발전량(PV시장잠재)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>REC랑 주요가정 수정해서, 다시 geocalculator</t>
   </si>
   <si>
@@ -542,6 +538,10 @@
   </si>
   <si>
     <t>2023년</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>발전량+(PV시장잠재)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1375,6 +1375,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1389,12 +1395,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1841,14 +1841,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F413839-46EB-4E86-9010-FD8440F93D28}">
   <dimension ref="A2:B4"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1856,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1864,7 +1864,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1875,11 +1875,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF530A9C-EEFD-4CCE-8F84-5BE1E43BE6A3}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="H1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1943,7 +1943,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="I5" s="84">
+      <c r="I5" s="79">
         <f>H4/E7</f>
         <v>4.7164106905308985E-2</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1988,9 +1988,15 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="F11" s="83">
+      <c r="F11" s="78">
         <f>E10-E4</f>
         <v>0.33786426886484999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="I12" s="79">
+        <f>E7/C4</f>
+        <v>0.35304662859753694</v>
       </c>
     </row>
   </sheetData>
@@ -2002,9 +2008,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3675085-88FF-4B84-8D84-84D85AD6A022}">
   <dimension ref="A1:Z90"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:26" ht="20.25">
+    <row r="1" spans="1:26" ht="21">
       <c r="A1" s="33" t="s">
         <v>94</v>
       </c>
@@ -2047,7 +2053,7 @@
       <c r="U2" s="35"/>
       <c r="V2" s="35"/>
     </row>
-    <row r="3" spans="1:26" ht="20.25">
+    <row r="3" spans="1:26" ht="21">
       <c r="B3" s="33" t="s">
         <v>95</v>
       </c>
@@ -2071,7 +2077,7 @@
       <c r="V3" s="34"/>
       <c r="Z3" s="36"/>
     </row>
-    <row r="4" spans="1:26" ht="21" thickBot="1">
+    <row r="4" spans="1:26" ht="21.5" thickBot="1">
       <c r="B4" s="33"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
@@ -2097,12 +2103,12 @@
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
       <c r="E5" s="38" t="s">
         <v>7</v>
       </c>
@@ -2157,18 +2163,18 @@
       <c r="V5" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="W5" s="78" t="s">
+      <c r="W5" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="X5" s="78"/>
-      <c r="Y5" s="78"/>
-      <c r="Z5" s="78"/>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="80"/>
+      <c r="Z5" s="80"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
       <c r="E6" s="41" t="s">
         <v>47</v>
       </c>
@@ -2223,10 +2229,10 @@
       <c r="V6" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="W6" s="79"/>
-      <c r="X6" s="79"/>
-      <c r="Y6" s="79"/>
-      <c r="Z6" s="79"/>
+      <c r="W6" s="81"/>
+      <c r="X6" s="81"/>
+      <c r="Y6" s="81"/>
+      <c r="Z6" s="81"/>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="44"/>
@@ -2943,7 +2949,7 @@
       </c>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="80" t="s">
+      <c r="A20" s="82" t="s">
         <v>101</v>
       </c>
       <c r="B20" s="44" t="s">
@@ -3010,12 +3016,12 @@
       </c>
       <c r="X20" s="44"/>
       <c r="Y20" s="44"/>
-      <c r="Z20" s="80" t="s">
+      <c r="Z20" s="82" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="80"/>
+      <c r="A21" s="82"/>
       <c r="B21" t="s">
         <v>105</v>
       </c>
@@ -3082,10 +3088,10 @@
       <c r="Y21" t="s">
         <v>99</v>
       </c>
-      <c r="Z21" s="80"/>
+      <c r="Z21" s="82"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="80"/>
+      <c r="A22" s="82"/>
       <c r="B22" t="s">
         <v>105</v>
       </c>
@@ -3152,10 +3158,10 @@
       <c r="Y22" t="s">
         <v>100</v>
       </c>
-      <c r="Z22" s="80"/>
+      <c r="Z22" s="82"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="80"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="44" t="s">
         <v>107</v>
       </c>
@@ -3220,10 +3226,10 @@
       </c>
       <c r="X23" s="57"/>
       <c r="Y23" s="57"/>
-      <c r="Z23" s="80"/>
+      <c r="Z23" s="82"/>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="80"/>
+      <c r="A24" s="82"/>
       <c r="B24" t="s">
         <v>105</v>
       </c>
@@ -3291,10 +3297,10 @@
       <c r="Y24" t="s">
         <v>99</v>
       </c>
-      <c r="Z24" s="80"/>
+      <c r="Z24" s="82"/>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="80"/>
+      <c r="A25" s="82"/>
       <c r="B25" t="s">
         <v>105</v>
       </c>
@@ -3362,10 +3368,10 @@
       <c r="Y25" t="s">
         <v>100</v>
       </c>
-      <c r="Z25" s="80"/>
+      <c r="Z25" s="82"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="80"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="44" t="s">
         <v>108</v>
       </c>
@@ -3430,10 +3436,10 @@
       </c>
       <c r="X26" s="44"/>
       <c r="Y26" s="44"/>
-      <c r="Z26" s="80"/>
+      <c r="Z26" s="82"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="80"/>
+      <c r="A27" s="82"/>
       <c r="D27" t="s">
         <v>99</v>
       </c>
@@ -3494,10 +3500,10 @@
       <c r="Y27" t="s">
         <v>99</v>
       </c>
-      <c r="Z27" s="80"/>
+      <c r="Z27" s="82"/>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="80"/>
+      <c r="A28" s="82"/>
       <c r="B28" t="s">
         <v>105</v>
       </c>
@@ -3564,10 +3570,10 @@
       <c r="Y28" t="s">
         <v>100</v>
       </c>
-      <c r="Z28" s="80"/>
+      <c r="Z28" s="82"/>
     </row>
     <row r="29" spans="1:26">
-      <c r="A29" s="80"/>
+      <c r="A29" s="82"/>
       <c r="B29" s="44" t="s">
         <v>109</v>
       </c>
@@ -3632,10 +3638,10 @@
       </c>
       <c r="X29" s="57"/>
       <c r="Y29" s="57"/>
-      <c r="Z29" s="80"/>
+      <c r="Z29" s="82"/>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="80"/>
+      <c r="A30" s="82"/>
       <c r="B30" s="58" t="s">
         <v>105</v>
       </c>
@@ -3704,10 +3710,10 @@
       <c r="Y30" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="Z30" s="80"/>
+      <c r="Z30" s="82"/>
     </row>
     <row r="31" spans="1:26">
-      <c r="A31" s="80"/>
+      <c r="A31" s="82"/>
       <c r="B31" s="44" t="s">
         <v>110</v>
       </c>
@@ -3772,10 +3778,10 @@
       </c>
       <c r="X31" s="44"/>
       <c r="Y31" s="44"/>
-      <c r="Z31" s="80"/>
+      <c r="Z31" s="82"/>
     </row>
     <row r="32" spans="1:26">
-      <c r="A32" s="80"/>
+      <c r="A32" s="82"/>
       <c r="B32" t="s">
         <v>105</v>
       </c>
@@ -3842,10 +3848,10 @@
       <c r="Y32" t="s">
         <v>99</v>
       </c>
-      <c r="Z32" s="80"/>
+      <c r="Z32" s="82"/>
     </row>
     <row r="33" spans="1:26">
-      <c r="A33" s="80"/>
+      <c r="A33" s="82"/>
       <c r="B33" t="s">
         <v>105</v>
       </c>
@@ -3912,10 +3918,10 @@
       <c r="Y33" t="s">
         <v>100</v>
       </c>
-      <c r="Z33" s="80"/>
+      <c r="Z33" s="82"/>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="80"/>
+      <c r="A34" s="82"/>
       <c r="B34" s="61" t="s">
         <v>105</v>
       </c>
@@ -3984,10 +3990,10 @@
         <v>111</v>
       </c>
       <c r="Y34" s="61"/>
-      <c r="Z34" s="80"/>
+      <c r="Z34" s="82"/>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="80"/>
+      <c r="A35" s="82"/>
       <c r="B35" t="s">
         <v>105</v>
       </c>
@@ -4054,10 +4060,10 @@
       <c r="Y35" t="s">
         <v>99</v>
       </c>
-      <c r="Z35" s="80"/>
+      <c r="Z35" s="82"/>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="80"/>
+      <c r="A36" s="82"/>
       <c r="B36" t="s">
         <v>105</v>
       </c>
@@ -4124,10 +4130,10 @@
       <c r="Y36" t="s">
         <v>100</v>
       </c>
-      <c r="Z36" s="80"/>
+      <c r="Z36" s="82"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="80"/>
+      <c r="A37" s="82"/>
       <c r="B37" s="61"/>
       <c r="C37" s="61" t="s">
         <v>112</v>
@@ -4192,10 +4198,10 @@
         <v>112</v>
       </c>
       <c r="Y37" s="61"/>
-      <c r="Z37" s="80"/>
+      <c r="Z37" s="82"/>
     </row>
     <row r="38" spans="1:26">
-      <c r="A38" s="80"/>
+      <c r="A38" s="82"/>
       <c r="D38" t="s">
         <v>99</v>
       </c>
@@ -4256,10 +4262,10 @@
       <c r="Y38" t="s">
         <v>99</v>
       </c>
-      <c r="Z38" s="80"/>
+      <c r="Z38" s="82"/>
     </row>
     <row r="39" spans="1:26">
-      <c r="A39" s="80"/>
+      <c r="A39" s="82"/>
       <c r="D39" t="s">
         <v>100</v>
       </c>
@@ -4320,10 +4326,10 @@
       <c r="Y39" t="s">
         <v>100</v>
       </c>
-      <c r="Z39" s="80"/>
+      <c r="Z39" s="82"/>
     </row>
     <row r="40" spans="1:26">
-      <c r="A40" s="80"/>
+      <c r="A40" s="82"/>
       <c r="B40" s="61"/>
       <c r="C40" s="61" t="s">
         <v>113</v>
@@ -4388,10 +4394,10 @@
         <v>113</v>
       </c>
       <c r="Y40" s="61"/>
-      <c r="Z40" s="80"/>
+      <c r="Z40" s="82"/>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="80"/>
+      <c r="A41" s="82"/>
       <c r="D41" t="s">
         <v>99</v>
       </c>
@@ -4452,10 +4458,10 @@
       <c r="Y41" t="s">
         <v>99</v>
       </c>
-      <c r="Z41" s="80"/>
+      <c r="Z41" s="82"/>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="80"/>
+      <c r="A42" s="82"/>
       <c r="D42" t="s">
         <v>100</v>
       </c>
@@ -4516,10 +4522,10 @@
       <c r="Y42" t="s">
         <v>100</v>
       </c>
-      <c r="Z42" s="80"/>
+      <c r="Z42" s="82"/>
     </row>
     <row r="43" spans="1:26">
-      <c r="A43" s="80"/>
+      <c r="A43" s="82"/>
       <c r="B43" s="61"/>
       <c r="C43" s="61" t="s">
         <v>114</v>
@@ -4584,10 +4590,10 @@
         <v>114</v>
       </c>
       <c r="Y43" s="61"/>
-      <c r="Z43" s="80"/>
+      <c r="Z43" s="82"/>
     </row>
     <row r="44" spans="1:26">
-      <c r="A44" s="80"/>
+      <c r="A44" s="82"/>
       <c r="D44" t="s">
         <v>99</v>
       </c>
@@ -4649,10 +4655,10 @@
       <c r="Y44" t="s">
         <v>99</v>
       </c>
-      <c r="Z44" s="80"/>
+      <c r="Z44" s="82"/>
     </row>
     <row r="45" spans="1:26">
-      <c r="A45" s="80"/>
+      <c r="A45" s="82"/>
       <c r="D45" t="s">
         <v>100</v>
       </c>
@@ -4713,10 +4719,10 @@
       <c r="Y45" t="s">
         <v>100</v>
       </c>
-      <c r="Z45" s="80"/>
+      <c r="Z45" s="82"/>
     </row>
     <row r="46" spans="1:26">
-      <c r="A46" s="80"/>
+      <c r="A46" s="82"/>
       <c r="B46" s="66"/>
       <c r="C46" s="61" t="s">
         <v>115</v>
@@ -4781,10 +4787,10 @@
         <v>115</v>
       </c>
       <c r="Y46" s="66"/>
-      <c r="Z46" s="80"/>
+      <c r="Z46" s="82"/>
     </row>
     <row r="47" spans="1:26">
-      <c r="A47" s="80"/>
+      <c r="A47" s="82"/>
       <c r="B47" t="s">
         <v>105</v>
       </c>
@@ -4851,10 +4857,10 @@
       <c r="Y47" t="s">
         <v>99</v>
       </c>
-      <c r="Z47" s="80"/>
+      <c r="Z47" s="82"/>
     </row>
     <row r="48" spans="1:26">
-      <c r="A48" s="80"/>
+      <c r="A48" s="82"/>
       <c r="D48" t="s">
         <v>100</v>
       </c>
@@ -4915,10 +4921,10 @@
       <c r="Y48" t="s">
         <v>100</v>
       </c>
-      <c r="Z48" s="80"/>
+      <c r="Z48" s="82"/>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="80"/>
+      <c r="A49" s="82"/>
       <c r="B49" s="61"/>
       <c r="C49" s="61" t="s">
         <v>116</v>
@@ -4983,10 +4989,10 @@
         <v>116</v>
       </c>
       <c r="Y49" s="61"/>
-      <c r="Z49" s="80"/>
+      <c r="Z49" s="82"/>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="80"/>
+      <c r="A50" s="82"/>
       <c r="B50" t="s">
         <v>105</v>
       </c>
@@ -5051,10 +5057,10 @@
       <c r="Y50" t="s">
         <v>100</v>
       </c>
-      <c r="Z50" s="80"/>
+      <c r="Z50" s="82"/>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="80"/>
+      <c r="A51" s="82"/>
       <c r="B51" s="61" t="s">
         <v>105</v>
       </c>
@@ -5123,10 +5129,10 @@
         <v>118</v>
       </c>
       <c r="Y51" s="61"/>
-      <c r="Z51" s="80"/>
+      <c r="Z51" s="82"/>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="80"/>
+      <c r="A52" s="82"/>
       <c r="D52" t="s">
         <v>99</v>
       </c>
@@ -5188,10 +5194,10 @@
       <c r="Y52" t="s">
         <v>99</v>
       </c>
-      <c r="Z52" s="80"/>
+      <c r="Z52" s="82"/>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="80"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="61"/>
       <c r="C53" s="61" t="s">
         <v>119</v>
@@ -5256,10 +5262,10 @@
         <v>119</v>
       </c>
       <c r="Y53" s="61"/>
-      <c r="Z53" s="80"/>
+      <c r="Z53" s="82"/>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="80"/>
+      <c r="A54" s="82"/>
       <c r="D54" t="s">
         <v>99</v>
       </c>
@@ -5320,10 +5326,10 @@
       <c r="Y54" t="s">
         <v>99</v>
       </c>
-      <c r="Z54" s="80"/>
+      <c r="Z54" s="82"/>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="80"/>
+      <c r="A55" s="82"/>
       <c r="D55" t="s">
         <v>100</v>
       </c>
@@ -5384,10 +5390,10 @@
       <c r="Y55" t="s">
         <v>100</v>
       </c>
-      <c r="Z55" s="80"/>
+      <c r="Z55" s="82"/>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="80"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="61"/>
       <c r="C56" s="61" t="s">
         <v>120</v>
@@ -5452,10 +5458,10 @@
         <v>120</v>
       </c>
       <c r="Y56" s="61"/>
-      <c r="Z56" s="80"/>
+      <c r="Z56" s="82"/>
     </row>
     <row r="57" spans="1:26">
-      <c r="A57" s="80"/>
+      <c r="A57" s="82"/>
       <c r="D57" t="s">
         <v>99</v>
       </c>
@@ -5516,10 +5522,10 @@
       <c r="Y57" t="s">
         <v>99</v>
       </c>
-      <c r="Z57" s="80"/>
+      <c r="Z57" s="82"/>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="80"/>
+      <c r="A58" s="82"/>
       <c r="B58" s="44" t="s">
         <v>121</v>
       </c>
@@ -5584,10 +5590,10 @@
       </c>
       <c r="X58" s="44"/>
       <c r="Y58" s="44"/>
-      <c r="Z58" s="80"/>
+      <c r="Z58" s="82"/>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="80"/>
+      <c r="A59" s="82"/>
       <c r="B59" t="s">
         <v>105</v>
       </c>
@@ -5654,10 +5660,10 @@
       <c r="Y59" t="s">
         <v>99</v>
       </c>
-      <c r="Z59" s="80"/>
+      <c r="Z59" s="82"/>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="80"/>
+      <c r="A60" s="82"/>
       <c r="B60" t="s">
         <v>105</v>
       </c>
@@ -5724,10 +5730,10 @@
       <c r="Y60" t="s">
         <v>100</v>
       </c>
-      <c r="Z60" s="80"/>
+      <c r="Z60" s="82"/>
     </row>
     <row r="61" spans="1:26">
-      <c r="A61" s="80"/>
+      <c r="A61" s="82"/>
       <c r="B61" s="61" t="s">
         <v>105</v>
       </c>
@@ -5796,10 +5802,10 @@
         <v>122</v>
       </c>
       <c r="Y61" s="61"/>
-      <c r="Z61" s="80"/>
+      <c r="Z61" s="82"/>
     </row>
     <row r="62" spans="1:26">
-      <c r="A62" s="80"/>
+      <c r="A62" s="82"/>
       <c r="B62" t="s">
         <v>105</v>
       </c>
@@ -5866,10 +5872,10 @@
       <c r="Y62" t="s">
         <v>99</v>
       </c>
-      <c r="Z62" s="80"/>
+      <c r="Z62" s="82"/>
     </row>
     <row r="63" spans="1:26">
-      <c r="A63" s="80"/>
+      <c r="A63" s="82"/>
       <c r="B63" t="s">
         <v>105</v>
       </c>
@@ -5936,10 +5942,10 @@
       <c r="Y63" t="s">
         <v>100</v>
       </c>
-      <c r="Z63" s="80"/>
+      <c r="Z63" s="82"/>
     </row>
     <row r="64" spans="1:26">
-      <c r="A64" s="80"/>
+      <c r="A64" s="82"/>
       <c r="B64" s="61" t="s">
         <v>105</v>
       </c>
@@ -6008,10 +6014,10 @@
         <v>123</v>
       </c>
       <c r="Y64" s="61"/>
-      <c r="Z64" s="80"/>
+      <c r="Z64" s="82"/>
     </row>
     <row r="65" spans="1:26">
-      <c r="A65" s="80"/>
+      <c r="A65" s="82"/>
       <c r="B65" t="s">
         <v>105</v>
       </c>
@@ -6078,10 +6084,10 @@
       <c r="Y65" t="s">
         <v>99</v>
       </c>
-      <c r="Z65" s="80"/>
+      <c r="Z65" s="82"/>
     </row>
     <row r="66" spans="1:26">
-      <c r="A66" s="80"/>
+      <c r="A66" s="82"/>
       <c r="B66" t="s">
         <v>105</v>
       </c>
@@ -6148,10 +6154,10 @@
       <c r="Y66" t="s">
         <v>100</v>
       </c>
-      <c r="Z66" s="80"/>
+      <c r="Z66" s="82"/>
     </row>
     <row r="67" spans="1:26">
-      <c r="A67" s="80"/>
+      <c r="A67" s="82"/>
       <c r="B67" s="61" t="s">
         <v>105</v>
       </c>
@@ -6220,10 +6226,10 @@
         <v>124</v>
       </c>
       <c r="Y67" s="61"/>
-      <c r="Z67" s="80"/>
+      <c r="Z67" s="82"/>
     </row>
     <row r="68" spans="1:26">
-      <c r="A68" s="80"/>
+      <c r="A68" s="82"/>
       <c r="B68" t="s">
         <v>105</v>
       </c>
@@ -6290,10 +6296,10 @@
       <c r="Y68" t="s">
         <v>99</v>
       </c>
-      <c r="Z68" s="80"/>
+      <c r="Z68" s="82"/>
     </row>
     <row r="69" spans="1:26">
-      <c r="A69" s="80"/>
+      <c r="A69" s="82"/>
       <c r="B69" t="s">
         <v>105</v>
       </c>
@@ -6360,10 +6366,10 @@
       <c r="Y69" t="s">
         <v>100</v>
       </c>
-      <c r="Z69" s="80"/>
+      <c r="Z69" s="82"/>
     </row>
     <row r="70" spans="1:26">
-      <c r="A70" s="80"/>
+      <c r="A70" s="82"/>
       <c r="B70" s="61"/>
       <c r="C70" s="61" t="s">
         <v>125</v>
@@ -6428,10 +6434,10 @@
         <v>125</v>
       </c>
       <c r="Y70" s="61"/>
-      <c r="Z70" s="80"/>
+      <c r="Z70" s="82"/>
     </row>
     <row r="71" spans="1:26">
-      <c r="A71" s="80"/>
+      <c r="A71" s="82"/>
       <c r="D71" t="s">
         <v>99</v>
       </c>
@@ -6492,10 +6498,10 @@
       <c r="Y71" t="s">
         <v>99</v>
       </c>
-      <c r="Z71" s="80"/>
+      <c r="Z71" s="82"/>
     </row>
     <row r="72" spans="1:26">
-      <c r="A72" s="80"/>
+      <c r="A72" s="82"/>
       <c r="D72" t="s">
         <v>100</v>
       </c>
@@ -6556,10 +6562,10 @@
       <c r="Y72" t="s">
         <v>100</v>
       </c>
-      <c r="Z72" s="80"/>
+      <c r="Z72" s="82"/>
     </row>
     <row r="73" spans="1:26">
-      <c r="A73" s="80"/>
+      <c r="A73" s="82"/>
       <c r="B73" s="61"/>
       <c r="C73" s="61" t="s">
         <v>126</v>
@@ -6624,10 +6630,10 @@
         <v>126</v>
       </c>
       <c r="Y73" s="61"/>
-      <c r="Z73" s="80"/>
+      <c r="Z73" s="82"/>
     </row>
     <row r="74" spans="1:26">
-      <c r="A74" s="80"/>
+      <c r="A74" s="82"/>
       <c r="D74" t="s">
         <v>100</v>
       </c>
@@ -6689,10 +6695,10 @@
       <c r="Y74" t="s">
         <v>100</v>
       </c>
-      <c r="Z74" s="80"/>
+      <c r="Z74" s="82"/>
     </row>
     <row r="75" spans="1:26">
-      <c r="A75" s="80"/>
+      <c r="A75" s="82"/>
       <c r="B75" s="61"/>
       <c r="C75" s="61" t="s">
         <v>127</v>
@@ -6757,10 +6763,10 @@
         <v>127</v>
       </c>
       <c r="Y75" s="61"/>
-      <c r="Z75" s="80"/>
+      <c r="Z75" s="82"/>
     </row>
     <row r="76" spans="1:26">
-      <c r="A76" s="80"/>
+      <c r="A76" s="82"/>
       <c r="D76" t="s">
         <v>99</v>
       </c>
@@ -6821,10 +6827,10 @@
       <c r="Y76" t="s">
         <v>99</v>
       </c>
-      <c r="Z76" s="80"/>
+      <c r="Z76" s="82"/>
     </row>
     <row r="77" spans="1:26">
-      <c r="A77" s="81" t="s">
+      <c r="A77" s="83" t="s">
         <v>103</v>
       </c>
       <c r="B77" s="69" t="s">
@@ -6891,12 +6897,12 @@
       </c>
       <c r="X77" s="69"/>
       <c r="Y77" s="69"/>
-      <c r="Z77" s="81" t="s">
+      <c r="Z77" s="83" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="78" spans="1:26">
-      <c r="A78" s="80"/>
+      <c r="A78" s="82"/>
       <c r="B78" t="s">
         <v>105</v>
       </c>
@@ -6963,10 +6969,10 @@
       <c r="Y78" t="s">
         <v>99</v>
       </c>
-      <c r="Z78" s="80"/>
+      <c r="Z78" s="82"/>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="80"/>
+      <c r="A79" s="82"/>
       <c r="B79" t="s">
         <v>105</v>
       </c>
@@ -7033,10 +7039,10 @@
       <c r="Y79" t="s">
         <v>100</v>
       </c>
-      <c r="Z79" s="80"/>
+      <c r="Z79" s="82"/>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="80"/>
+      <c r="A80" s="82"/>
       <c r="B80" s="44" t="s">
         <v>129</v>
       </c>
@@ -7101,10 +7107,10 @@
       </c>
       <c r="X80" s="44"/>
       <c r="Y80" s="44"/>
-      <c r="Z80" s="80"/>
-    </row>
-    <row r="81" spans="1:26" ht="17.25" thickBot="1">
-      <c r="A81" s="82"/>
+      <c r="Z80" s="82"/>
+    </row>
+    <row r="81" spans="1:26" ht="17.5" thickBot="1">
+      <c r="A81" s="84"/>
       <c r="B81" s="73"/>
       <c r="C81" s="73"/>
       <c r="D81" s="73" t="s">
@@ -7169,7 +7175,7 @@
       <c r="Y81" s="73" t="s">
         <v>99</v>
       </c>
-      <c r="Z81" s="82"/>
+      <c r="Z81" s="84"/>
     </row>
     <row r="82" spans="1:26">
       <c r="E82" s="35"/>
@@ -7392,19 +7398,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7F234A-43A7-4A1E-B6E3-9F072D6F2695}">
   <dimension ref="A1:U38"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="19" width="10.75" style="3" customWidth="1"/>
-    <col min="20" max="20" width="17.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.125" style="3"/>
+    <col min="20" max="20" width="17.08203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.08203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="19.5">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="20.5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="14.25" thickBot="1">
+    <row r="3" spans="1:20" ht="16.5" thickBot="1">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -7470,7 +7476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="14.25" thickBot="1">
+    <row r="5" spans="1:20" ht="16.5" thickBot="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
         <v>25</v>
@@ -7527,7 +7533,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="14.25" thickTop="1">
+    <row r="6" spans="1:20" ht="16.5" thickTop="1">
       <c r="A6" s="13">
         <v>1991</v>
       </c>
@@ -9387,7 +9393,7 @@
       </c>
       <c r="T36" s="15"/>
     </row>
-    <row r="37" spans="1:21" s="24" customFormat="1" ht="14.25" thickBot="1">
+    <row r="37" spans="1:21" s="24" customFormat="1" ht="16.5" thickBot="1">
       <c r="A37" s="26">
         <v>2022</v>
       </c>
@@ -9469,9 +9475,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9922FD-DCA2-4B12-A090-21295F7ECBE3}">
   <dimension ref="A1:T82"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.08203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="9.125" style="3"/>
+    <col min="1" max="16384" width="9.08203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
